--- a/12608016.xlsx
+++ b/12608016.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/DD440DD7F90BF0F9/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dd440dd7f90bf0f9/Desktop/demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D7A846C-3CB0-456B-825F-8FDAA5D08C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{8D7A846C-3CB0-456B-825F-8FDAA5D08C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04E9213C-0F60-4F80-9EB2-442CA7898444}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -204,6 +203,15 @@
   </si>
   <si>
     <t>felt exhausted, low and sleepy</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>sleepy all day</t>
   </si>
 </sst>
 </file>
@@ -1028,26 +1036,48 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
-        <f t="shared" ref="I6:I69" si="1">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+      <c r="A7" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B7" s="14">
+        <v>400</v>
+      </c>
+      <c r="C7" s="14">
+        <v>45</v>
+      </c>
+      <c r="D7" s="14">
+        <v>60</v>
+      </c>
+      <c r="E7" s="14">
+        <v>60</v>
+      </c>
+      <c r="F7" s="14">
+        <v>350</v>
+      </c>
+      <c r="G7" s="14">
+        <v>7</v>
+      </c>
+      <c r="H7" s="14">
+        <v>30</v>
+      </c>
+      <c r="I7" s="15">
+        <v>945</v>
+      </c>
+      <c r="J7" s="15">
+        <v>495</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>
@@ -1059,7 +1089,7 @@
       <c r="G8" s="14"/>
       <c r="H8" s="14"/>
       <c r="I8" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="I7:I69" si="1">IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
         <v/>
       </c>
       <c r="J8" s="15" t="str">

--- a/12608016.xlsx
+++ b/12608016.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dd440dd7f90bf0f9/Desktop/demo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dd440dd7f90bf0f9/Desktop/demo/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{8D7A846C-3CB0-456B-825F-8FDAA5D08C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04E9213C-0F60-4F80-9EB2-442CA7898444}"/>
+  <xr:revisionPtr revIDLastSave="224" documentId="8_{8D7A846C-3CB0-456B-825F-8FDAA5D08C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BA3C8E9-2457-4B26-8848-A959F7FD0A15}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -212,6 +212,54 @@
   </si>
   <si>
     <t>sleepy all day</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>relaxing day</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>good study session</t>
+  </si>
+  <si>
+    <t>felt sleepy</t>
+  </si>
+  <si>
+    <t>productive weekend</t>
+  </si>
+  <si>
+    <t>relaxed day</t>
+  </si>
+  <si>
+    <t>normal college day</t>
+  </si>
+  <si>
+    <t>productive day</t>
+  </si>
+  <si>
+    <t>quite tired</t>
+  </si>
+  <si>
+    <t>good concentration</t>
+  </si>
+  <si>
+    <t>couldn't focus much</t>
+  </si>
+  <si>
+    <t>mostly rested</t>
+  </si>
+  <si>
+    <t>average day</t>
+  </si>
+  <si>
+    <t>completed some tasks</t>
   </si>
 </sst>
 </file>
@@ -492,6 +540,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1061,9 +1113,11 @@
         <v>30</v>
       </c>
       <c r="I7" s="15">
+        <f t="shared" ref="I7:I69" si="1">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
         <v>945</v>
       </c>
       <c r="J7" s="15">
+        <f t="shared" si="0"/>
         <v>495</v>
       </c>
       <c r="K7" s="16" t="s">
@@ -1080,365 +1134,755 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
-        <f t="shared" ref="I7:I69" si="1">IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B8" s="14">
+        <v>420</v>
+      </c>
+      <c r="C8" s="14">
+        <v>20</v>
+      </c>
+      <c r="D8" s="14">
+        <v>45</v>
+      </c>
+      <c r="E8" s="14">
+        <v>45</v>
+      </c>
+      <c r="F8" s="14">
+        <v>200</v>
+      </c>
+      <c r="G8" s="14">
+        <v>4</v>
+      </c>
+      <c r="H8" s="14">
+        <v>60</v>
+      </c>
+      <c r="I8" s="15">
+        <f t="shared" si="1"/>
+        <v>790</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>650</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B9" s="14">
+        <v>450</v>
+      </c>
+      <c r="C9" s="14">
+        <v>30</v>
+      </c>
+      <c r="D9" s="14">
+        <v>75</v>
+      </c>
+      <c r="E9" s="14">
+        <v>60</v>
+      </c>
+      <c r="F9" s="14">
+        <v>250</v>
+      </c>
+      <c r="G9" s="14">
+        <v>5</v>
+      </c>
+      <c r="H9" s="14">
+        <v>45</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B10" s="14">
+        <v>390</v>
+      </c>
+      <c r="C10" s="14">
+        <v>15</v>
+      </c>
+      <c r="D10" s="14">
+        <v>60</v>
+      </c>
+      <c r="E10" s="14">
+        <v>45</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>30</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>540</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>900</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B11" s="14">
+        <v>480</v>
+      </c>
+      <c r="C11" s="14">
+        <v>45</v>
+      </c>
+      <c r="D11" s="14">
+        <v>90</v>
+      </c>
+      <c r="E11" s="14">
+        <v>60</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>60</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>735</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>705</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B12" s="14">
+        <v>510</v>
+      </c>
+      <c r="C12" s="14">
+        <v>30</v>
+      </c>
+      <c r="D12" s="14">
+        <v>75</v>
+      </c>
+      <c r="E12" s="14">
+        <v>45</v>
+      </c>
+      <c r="F12" s="14">
+        <v>300</v>
+      </c>
+      <c r="G12" s="14">
+        <v>6</v>
+      </c>
+      <c r="H12" s="14">
+        <v>60</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B13" s="14">
+        <v>420</v>
+      </c>
+      <c r="C13" s="14">
+        <v>20</v>
+      </c>
+      <c r="D13" s="14">
+        <v>90</v>
+      </c>
+      <c r="E13" s="14">
+        <v>60</v>
+      </c>
+      <c r="F13" s="14">
+        <v>200</v>
+      </c>
+      <c r="G13" s="14">
+        <v>4</v>
+      </c>
+      <c r="H13" s="14">
+        <v>45</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>835</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>605</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B14" s="14">
+        <v>435</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>90</v>
+      </c>
+      <c r="E14" s="14">
+        <v>75</v>
+      </c>
+      <c r="F14" s="14">
+        <v>400</v>
+      </c>
+      <c r="G14" s="14">
+        <v>8</v>
+      </c>
+      <c r="H14" s="14">
+        <v>45</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1075</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>365</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B15" s="14">
+        <v>400</v>
+      </c>
+      <c r="C15" s="14">
+        <v>15</v>
+      </c>
+      <c r="D15" s="14">
+        <v>60</v>
+      </c>
+      <c r="E15" s="14">
+        <v>45</v>
+      </c>
+      <c r="F15" s="14">
+        <v>200</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
+        <v>45</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>765</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>675</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B16" s="14">
+        <v>450</v>
+      </c>
+      <c r="C16" s="14">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14">
+        <v>90</v>
+      </c>
+      <c r="E16" s="14">
+        <v>75</v>
+      </c>
+      <c r="F16" s="14">
+        <v>250</v>
+      </c>
+      <c r="G16" s="14">
+        <v>5</v>
+      </c>
+      <c r="H16" s="14">
+        <v>30</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>925</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>515</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B17" s="14">
+        <v>390</v>
+      </c>
+      <c r="C17" s="14">
+        <v>15</v>
+      </c>
+      <c r="D17" s="14">
+        <v>45</v>
+      </c>
+      <c r="E17" s="14">
+        <v>45</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>30</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>525</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>915</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B18" s="14">
+        <v>480</v>
+      </c>
+      <c r="C18" s="14">
+        <v>45</v>
+      </c>
+      <c r="D18" s="14">
+        <v>90</v>
+      </c>
+      <c r="E18" s="14">
+        <v>75</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>60</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>690</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B19" s="14">
+        <v>510</v>
+      </c>
+      <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>75</v>
+      </c>
+      <c r="E19" s="14">
+        <v>45</v>
+      </c>
+      <c r="F19" s="14">
+        <v>300</v>
+      </c>
+      <c r="G19" s="14">
+        <v>6</v>
+      </c>
+      <c r="H19" s="14">
+        <v>60</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B20" s="14">
+        <v>420</v>
+      </c>
+      <c r="C20" s="14">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>90</v>
+      </c>
+      <c r="E20" s="14">
+        <v>75</v>
+      </c>
+      <c r="F20" s="14">
+        <v>200</v>
+      </c>
+      <c r="G20" s="14">
+        <v>4</v>
+      </c>
+      <c r="H20" s="14">
+        <v>45</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B21" s="14">
+        <v>435</v>
+      </c>
+      <c r="C21" s="14">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14">
+        <v>90</v>
+      </c>
+      <c r="E21" s="14">
+        <v>75</v>
+      </c>
+      <c r="F21" s="14">
+        <v>400</v>
+      </c>
+      <c r="G21" s="14">
+        <v>8</v>
+      </c>
+      <c r="H21" s="14">
+        <v>45</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1075</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>365</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B22" s="14">
+        <v>405</v>
+      </c>
+      <c r="C22" s="14">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
+        <v>90</v>
+      </c>
+      <c r="E22" s="14">
+        <v>75</v>
+      </c>
+      <c r="F22" s="14">
+        <v>250</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="14">
+        <v>45</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>885</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>555</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B23" s="14">
+        <v>450</v>
+      </c>
+      <c r="C23" s="14">
+        <v>30</v>
+      </c>
+      <c r="D23" s="14">
+        <v>75</v>
+      </c>
+      <c r="E23" s="14">
+        <v>60</v>
+      </c>
+      <c r="F23" s="14">
+        <v>250</v>
+      </c>
+      <c r="G23" s="14">
+        <v>5</v>
+      </c>
+      <c r="H23" s="14">
+        <v>45</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
+      <c r="A24" s="13">
+        <v>46270</v>
+      </c>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
       <c r="H24" s="14"/>
       <c r="I24" s="15" t="str">
         <f t="shared" si="1"/>

--- a/12608016.xlsx
+++ b/12608016.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dd440dd7f90bf0f9/Desktop/demo/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="224" documentId="8_{8D7A846C-3CB0-456B-825F-8FDAA5D08C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BA3C8E9-2457-4B26-8848-A959F7FD0A15}"/>
+  <xr:revisionPtr revIDLastSave="228" documentId="8_{8D7A846C-3CB0-456B-825F-8FDAA5D08C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61920803-9652-4EF4-8FE8-358DCFF28938}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1866,7 +1866,7 @@
         <v>53</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1877,12 +1877,8 @@
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14">
-        <v>0</v>
-      </c>
-      <c r="G24" s="14">
-        <v>0</v>
-      </c>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
       <c r="H24" s="14"/>
       <c r="I24" s="15" t="str">
         <f t="shared" si="1"/>

--- a/12608016.xlsx
+++ b/12608016.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dd440dd7f90bf0f9/Desktop/demo/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="228" documentId="8_{8D7A846C-3CB0-456B-825F-8FDAA5D08C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61920803-9652-4EF4-8FE8-358DCFF28938}"/>
+  <xr:revisionPtr revIDLastSave="239" documentId="8_{8D7A846C-3CB0-456B-825F-8FDAA5D08C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED572E7E-89D1-4030-AF43-12585FD8D6FC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>completed some tasks</t>
+  </si>
+  <si>
+    <t>didn't study much but felt nice</t>
   </si>
 </sst>
 </file>
@@ -1873,25 +1876,47 @@
       <c r="A24" s="13">
         <v>46270</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="B24" s="14">
+        <v>450</v>
+      </c>
+      <c r="C24" s="14">
+        <v>30</v>
+      </c>
+      <c r="D24" s="14">
+        <v>60</v>
+      </c>
+      <c r="E24" s="14">
+        <v>60</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>60</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>780</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/12608016.xlsx
+++ b/12608016.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dd440dd7f90bf0f9/Desktop/demo/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="239" documentId="8_{8D7A846C-3CB0-456B-825F-8FDAA5D08C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED572E7E-89D1-4030-AF43-12585FD8D6FC}"/>
+  <xr:revisionPtr revIDLastSave="267" documentId="8_{8D7A846C-3CB0-456B-825F-8FDAA5D08C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F21CB544-8A65-4282-83F0-A0FD9CC9A83E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,12 @@
   </si>
   <si>
     <t>didn't study much but felt nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">studied SQL </t>
+  </si>
+  <si>
+    <t>performed well in both CA</t>
   </si>
 </sst>
 </file>
@@ -1919,48 +1925,96 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B25" s="14">
+        <v>400</v>
+      </c>
+      <c r="C25" s="14">
+        <v>30</v>
+      </c>
+      <c r="D25" s="14">
+        <v>120</v>
+      </c>
+      <c r="E25" s="14">
+        <v>30</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>60</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>640</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>800</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B26" s="14">
+        <v>420</v>
+      </c>
+      <c r="C26" s="14">
+        <v>30</v>
+      </c>
+      <c r="D26" s="14">
+        <v>30</v>
+      </c>
+      <c r="E26" s="14">
+        <v>20</v>
+      </c>
+      <c r="F26" s="14">
+        <v>300</v>
+      </c>
+      <c r="G26" s="14">
+        <v>6</v>
+      </c>
+      <c r="H26" s="14">
+        <v>60</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>
